--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131046824</v>
+        <v>131046825</v>
       </c>
       <c r="B2" t="n">
         <v>79244</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401653</v>
+        <v>401650</v>
       </c>
       <c r="R2" t="n">
-        <v>6818054</v>
+        <v>6818017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131046825</v>
+        <v>131046824</v>
       </c>
       <c r="B3" t="n">
         <v>79244</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401650</v>
+        <v>401653</v>
       </c>
       <c r="R3" t="n">
-        <v>6818017</v>
+        <v>6818054</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046822</v>
+        <v>131047013</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,34 +1351,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401699</v>
+        <v>401631</v>
       </c>
       <c r="R8" t="n">
-        <v>6818070</v>
+        <v>6817903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,14 +1425,19 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1447,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131047013</v>
+        <v>131046822</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,39 +1468,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401631</v>
+        <v>401699</v>
       </c>
       <c r="R9" t="n">
-        <v>6817903</v>
+        <v>6818070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,19 +1537,14 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046828</v>
+        <v>131046769</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,34 +1799,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401634</v>
+        <v>401575</v>
       </c>
       <c r="R12" t="n">
-        <v>6817871</v>
+        <v>6817873</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1873,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046769</v>
+        <v>131046828</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,39 +1916,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401575</v>
+        <v>401634</v>
       </c>
       <c r="R13" t="n">
-        <v>6817873</v>
+        <v>6817871</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,12 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131046766</v>
+        <v>131047034</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>78647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,42 +2685,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401318</v>
+        <v>401597</v>
       </c>
       <c r="R20" t="n">
-        <v>6818379</v>
+        <v>6817852</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2752,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,12 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2794,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131047034</v>
+        <v>131046766</v>
       </c>
       <c r="B21" t="n">
-        <v>78647</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,34 +2792,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401597</v>
+        <v>401318</v>
       </c>
       <c r="R21" t="n">
-        <v>6817852</v>
+        <v>6818379</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2874,7 +2869,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131047014</v>
+        <v>131046832</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,39 +3233,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401378</v>
+        <v>401350</v>
       </c>
       <c r="R25" t="n">
-        <v>6818082</v>
+        <v>6818162</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3297,7 +3292,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3307,19 +3302,14 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3339,7 +3329,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131046832</v>
+        <v>131046826</v>
       </c>
       <c r="B26" t="n">
         <v>79244</v>
@@ -3374,10 +3364,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401350</v>
+        <v>401647</v>
       </c>
       <c r="R26" t="n">
-        <v>6818162</v>
+        <v>6817965</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3409,7 +3399,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3419,7 +3409,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3446,10 +3436,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131046826</v>
+        <v>131047014</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,34 +3447,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401647</v>
+        <v>401378</v>
       </c>
       <c r="R27" t="n">
-        <v>6817965</v>
+        <v>6818082</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3511,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,14 +3521,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131046825</v>
+        <v>131046824</v>
       </c>
       <c r="B2" t="n">
         <v>79244</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401650</v>
+        <v>401653</v>
       </c>
       <c r="R2" t="n">
-        <v>6818017</v>
+        <v>6818054</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131046824</v>
+        <v>131046825</v>
       </c>
       <c r="B3" t="n">
         <v>79244</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401653</v>
+        <v>401650</v>
       </c>
       <c r="R3" t="n">
-        <v>6818054</v>
+        <v>6818017</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131047013</v>
+        <v>131046822</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,39 +1351,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401631</v>
+        <v>401699</v>
       </c>
       <c r="R8" t="n">
-        <v>6817903</v>
+        <v>6818070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,19 +1420,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1457,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046822</v>
+        <v>131047013</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,34 +1458,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401699</v>
+        <v>401631</v>
       </c>
       <c r="R9" t="n">
-        <v>6818070</v>
+        <v>6817903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,14 +1532,19 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046769</v>
+        <v>131046828</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,39 +1799,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401575</v>
+        <v>401634</v>
       </c>
       <c r="R12" t="n">
-        <v>6817873</v>
+        <v>6817871</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1873,12 +1868,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046828</v>
+        <v>131046769</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,34 +1906,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401634</v>
+        <v>401575</v>
       </c>
       <c r="R13" t="n">
-        <v>6817871</v>
+        <v>6817873</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1985,7 +1980,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131047034</v>
+        <v>131046799</v>
       </c>
       <c r="B20" t="n">
-        <v>78647</v>
+        <v>78256</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401597</v>
+        <v>401649</v>
       </c>
       <c r="R20" t="n">
-        <v>6817852</v>
+        <v>6818014</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2901,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131046799</v>
+        <v>131047034</v>
       </c>
       <c r="B22" t="n">
-        <v>78256</v>
+        <v>78647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,21 +2912,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>401649</v>
+        <v>401597</v>
       </c>
       <c r="R22" t="n">
-        <v>6818014</v>
+        <v>6817852</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3329,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131046826</v>
+        <v>131047014</v>
       </c>
       <c r="B26" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,34 +3340,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401647</v>
+        <v>401378</v>
       </c>
       <c r="R26" t="n">
-        <v>6817965</v>
+        <v>6818082</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3399,7 +3404,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3409,14 +3414,19 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3436,10 +3446,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131047014</v>
+        <v>131046826</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,39 +3457,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401378</v>
+        <v>401647</v>
       </c>
       <c r="R27" t="n">
-        <v>6818082</v>
+        <v>6817965</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3511,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3521,19 +3526,14 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131046824</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131046825</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131046829</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>131046830</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>131046822</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046823</v>
+        <v>131046773</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,34 +1575,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401661</v>
+        <v>401346</v>
       </c>
       <c r="R10" t="n">
-        <v>6818064</v>
+        <v>6818162</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1639,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1649,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046773</v>
+        <v>131046823</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,39 +1692,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401346</v>
+        <v>401661</v>
       </c>
       <c r="R11" t="n">
-        <v>6818162</v>
+        <v>6818064</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,12 +1761,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,7 +1791,7 @@
         <v>131046828</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>131046709</v>
       </c>
       <c r="B14" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046724</v>
+        <v>131046708</v>
       </c>
       <c r="B16" t="n">
-        <v>79276</v>
+        <v>83225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401635</v>
+        <v>401645</v>
       </c>
       <c r="R16" t="n">
-        <v>6817874</v>
+        <v>6818016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131046708</v>
+        <v>131046724</v>
       </c>
       <c r="B17" t="n">
-        <v>83224</v>
+        <v>79277</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401645</v>
+        <v>401635</v>
       </c>
       <c r="R17" t="n">
-        <v>6818016</v>
+        <v>6817874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2453,7 +2453,7 @@
         <v>131046827</v>
       </c>
       <c r="B18" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131046799</v>
+        <v>131047034</v>
       </c>
       <c r="B20" t="n">
-        <v>78256</v>
+        <v>78648</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401649</v>
+        <v>401597</v>
       </c>
       <c r="R20" t="n">
-        <v>6818014</v>
+        <v>6817852</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131046766</v>
+        <v>131046799</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>78257</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,42 +2792,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401318</v>
+        <v>401649</v>
       </c>
       <c r="R21" t="n">
-        <v>6818379</v>
+        <v>6818014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2859,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,12 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131047034</v>
+        <v>131046766</v>
       </c>
       <c r="B22" t="n">
-        <v>78647</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,34 +2899,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>401597</v>
+        <v>401318</v>
       </c>
       <c r="R22" t="n">
-        <v>6817852</v>
+        <v>6818379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2981,7 +2976,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3011,7 +3011,7 @@
         <v>131046831</v>
       </c>
       <c r="B23" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>131046833</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>131046832</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131047014</v>
+        <v>131046826</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,39 +3340,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401378</v>
+        <v>401647</v>
       </c>
       <c r="R26" t="n">
-        <v>6818082</v>
+        <v>6817965</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3404,7 +3399,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3414,19 +3409,14 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3446,10 +3436,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131046826</v>
+        <v>131047014</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,34 +3447,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401647</v>
+        <v>401378</v>
       </c>
       <c r="R27" t="n">
-        <v>6817965</v>
+        <v>6818082</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3511,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,14 +3521,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -2236,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046708</v>
+        <v>131046724</v>
       </c>
       <c r="B16" t="n">
-        <v>83225</v>
+        <v>79277</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401645</v>
+        <v>401635</v>
       </c>
       <c r="R16" t="n">
-        <v>6818016</v>
+        <v>6817874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131046724</v>
+        <v>131046708</v>
       </c>
       <c r="B17" t="n">
-        <v>79277</v>
+        <v>83225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401635</v>
+        <v>401645</v>
       </c>
       <c r="R17" t="n">
-        <v>6817874</v>
+        <v>6818016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131046799</v>
+        <v>131046766</v>
       </c>
       <c r="B21" t="n">
-        <v>78257</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,34 +2792,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401649</v>
+        <v>401318</v>
       </c>
       <c r="R21" t="n">
-        <v>6818014</v>
+        <v>6818379</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2869,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131046766</v>
+        <v>131046799</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>78257</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,42 +2912,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>401318</v>
+        <v>401649</v>
       </c>
       <c r="R22" t="n">
-        <v>6818379</v>
+        <v>6818014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,7 +2971,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2976,12 +2981,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046773</v>
+        <v>131046823</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,39 +1575,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401346</v>
+        <v>401661</v>
       </c>
       <c r="R10" t="n">
-        <v>6818162</v>
+        <v>6818064</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,12 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046823</v>
+        <v>131046773</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,34 +1682,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401661</v>
+        <v>401346</v>
       </c>
       <c r="R11" t="n">
-        <v>6818064</v>
+        <v>6818162</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,7 +1756,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131046766</v>
+        <v>131046799</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>78257</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,42 +2792,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401318</v>
+        <v>401649</v>
       </c>
       <c r="R21" t="n">
-        <v>6818379</v>
+        <v>6818014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2859,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,12 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131046799</v>
+        <v>131046766</v>
       </c>
       <c r="B22" t="n">
-        <v>78257</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,34 +2899,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>401649</v>
+        <v>401318</v>
       </c>
       <c r="R22" t="n">
-        <v>6818014</v>
+        <v>6818379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2981,7 +2976,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131046830</v>
+        <v>131046772</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,34 +1127,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401538</v>
+        <v>401507</v>
       </c>
       <c r="R6" t="n">
-        <v>6818009</v>
+        <v>6818011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1201,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131046772</v>
+        <v>131046830</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,39 +1244,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>401507</v>
+        <v>401538</v>
       </c>
       <c r="R7" t="n">
-        <v>6818011</v>
+        <v>6818009</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,12 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046822</v>
+        <v>131047013</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,34 +1351,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401699</v>
+        <v>401631</v>
       </c>
       <c r="R8" t="n">
-        <v>6818070</v>
+        <v>6817903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,14 +1425,19 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1447,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131047013</v>
+        <v>131046822</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,39 +1468,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401631</v>
+        <v>401699</v>
       </c>
       <c r="R9" t="n">
-        <v>6817903</v>
+        <v>6818070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,19 +1537,14 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131046799</v>
+        <v>131046766</v>
       </c>
       <c r="B21" t="n">
-        <v>78257</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,34 +2792,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401649</v>
+        <v>401318</v>
       </c>
       <c r="R21" t="n">
-        <v>6818014</v>
+        <v>6818379</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2869,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131046766</v>
+        <v>131046799</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>78257</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,42 +2912,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>401318</v>
+        <v>401649</v>
       </c>
       <c r="R22" t="n">
-        <v>6818379</v>
+        <v>6818014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,7 +2971,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2976,12 +2981,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,7 +3008,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131046831</v>
+        <v>131046833</v>
       </c>
       <c r="B23" t="n">
         <v>79245</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>401378</v>
+        <v>401322</v>
       </c>
       <c r="R23" t="n">
-        <v>6818089</v>
+        <v>6818367</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,7 +3115,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131046833</v>
+        <v>131046831</v>
       </c>
       <c r="B24" t="n">
         <v>79245</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401322</v>
+        <v>401378</v>
       </c>
       <c r="R24" t="n">
-        <v>6818367</v>
+        <v>6818089</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131046832</v>
+        <v>131047014</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,34 +3233,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401350</v>
+        <v>401378</v>
       </c>
       <c r="R25" t="n">
-        <v>6818162</v>
+        <v>6818082</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3292,7 +3297,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3302,14 +3307,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3329,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131046826</v>
+        <v>131046832</v>
       </c>
       <c r="B26" t="n">
         <v>79245</v>
@@ -3364,10 +3374,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401647</v>
+        <v>401350</v>
       </c>
       <c r="R26" t="n">
-        <v>6817965</v>
+        <v>6818162</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3399,7 +3409,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3409,7 +3419,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3436,10 +3446,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131047014</v>
+        <v>131046826</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,39 +3457,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401378</v>
+        <v>401647</v>
       </c>
       <c r="R27" t="n">
-        <v>6818082</v>
+        <v>6817965</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3511,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3521,19 +3526,14 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131046824</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131046825</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131046829</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131046772</v>
+        <v>131046830</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,39 +1127,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401507</v>
+        <v>401538</v>
       </c>
       <c r="R6" t="n">
-        <v>6818011</v>
+        <v>6818009</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,12 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131046830</v>
+        <v>131046772</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,34 +1234,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>401538</v>
+        <v>401507</v>
       </c>
       <c r="R7" t="n">
-        <v>6818009</v>
+        <v>6818011</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1308,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131047013</v>
+        <v>131046822</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,39 +1351,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401631</v>
+        <v>401699</v>
       </c>
       <c r="R8" t="n">
-        <v>6817903</v>
+        <v>6818070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,19 +1420,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1457,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046822</v>
+        <v>131047013</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,34 +1458,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401699</v>
+        <v>401631</v>
       </c>
       <c r="R9" t="n">
-        <v>6818070</v>
+        <v>6817903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,14 +1532,19 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1567,7 +1567,7 @@
         <v>131046823</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046828</v>
+        <v>131046769</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,34 +1799,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401634</v>
+        <v>401575</v>
       </c>
       <c r="R12" t="n">
-        <v>6817871</v>
+        <v>6817873</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1873,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046769</v>
+        <v>131046828</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,39 +1916,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401575</v>
+        <v>401634</v>
       </c>
       <c r="R13" t="n">
-        <v>6817873</v>
+        <v>6817871</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,12 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,7 +2015,7 @@
         <v>131046709</v>
       </c>
       <c r="B14" t="n">
-        <v>83225</v>
+        <v>83226</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>131046724</v>
       </c>
       <c r="B16" t="n">
-        <v>79277</v>
+        <v>79278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>131046708</v>
       </c>
       <c r="B17" t="n">
-        <v>83225</v>
+        <v>83226</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>131046827</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>131047034</v>
       </c>
       <c r="B20" t="n">
-        <v>78648</v>
+        <v>78649</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>131046799</v>
       </c>
       <c r="B22" t="n">
-        <v>78257</v>
+        <v>78258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131046833</v>
+        <v>131046831</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>401322</v>
+        <v>401378</v>
       </c>
       <c r="R23" t="n">
-        <v>6818367</v>
+        <v>6818089</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,10 +3115,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131046831</v>
+        <v>131046833</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401378</v>
+        <v>401322</v>
       </c>
       <c r="R24" t="n">
-        <v>6818089</v>
+        <v>6818367</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131047014</v>
+        <v>131046832</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,39 +3233,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401378</v>
+        <v>401350</v>
       </c>
       <c r="R25" t="n">
-        <v>6818082</v>
+        <v>6818162</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3297,7 +3292,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3307,19 +3302,14 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3339,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131046832</v>
+        <v>131046826</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,10 +3364,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401350</v>
+        <v>401647</v>
       </c>
       <c r="R26" t="n">
-        <v>6818162</v>
+        <v>6817965</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3409,7 +3399,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3419,7 +3409,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3446,10 +3436,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131046826</v>
+        <v>131047014</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,34 +3447,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401647</v>
+        <v>401378</v>
       </c>
       <c r="R27" t="n">
-        <v>6817965</v>
+        <v>6818082</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3511,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,14 +3521,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1788,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046769</v>
+        <v>131046828</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,39 +1799,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401575</v>
+        <v>401634</v>
       </c>
       <c r="R12" t="n">
-        <v>6817873</v>
+        <v>6817871</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1873,12 +1868,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046828</v>
+        <v>131046769</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,34 +1906,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401634</v>
+        <v>401575</v>
       </c>
       <c r="R13" t="n">
-        <v>6817871</v>
+        <v>6817873</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1985,7 +1980,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,10 +2012,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046709</v>
+        <v>131046771</v>
       </c>
       <c r="B14" t="n">
-        <v>83226</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,34 +2023,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>401646</v>
+        <v>401556</v>
       </c>
       <c r="R14" t="n">
-        <v>6817967</v>
+        <v>6817954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2092,7 +2097,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,10 +2129,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046771</v>
+        <v>131046709</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>83226</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,39 +2140,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401556</v>
+        <v>401646</v>
       </c>
       <c r="R15" t="n">
-        <v>6817954</v>
+        <v>6817967</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,12 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046724</v>
+        <v>131046708</v>
       </c>
       <c r="B16" t="n">
-        <v>79278</v>
+        <v>83226</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401635</v>
+        <v>401645</v>
       </c>
       <c r="R16" t="n">
-        <v>6817874</v>
+        <v>6818016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131046708</v>
+        <v>131046724</v>
       </c>
       <c r="B17" t="n">
-        <v>83226</v>
+        <v>79278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401645</v>
+        <v>401635</v>
       </c>
       <c r="R17" t="n">
-        <v>6818016</v>
+        <v>6817874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3008,7 +3008,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131046831</v>
+        <v>131046833</v>
       </c>
       <c r="B23" t="n">
         <v>79246</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>401378</v>
+        <v>401322</v>
       </c>
       <c r="R23" t="n">
-        <v>6818089</v>
+        <v>6818367</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,7 +3115,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131046833</v>
+        <v>131046831</v>
       </c>
       <c r="B24" t="n">
         <v>79246</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401322</v>
+        <v>401378</v>
       </c>
       <c r="R24" t="n">
-        <v>6818367</v>
+        <v>6818089</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131046824</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131046825</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131046829</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131046765</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>131046830</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>131046772</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046822</v>
+        <v>131047013</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,34 +1351,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401699</v>
+        <v>401631</v>
       </c>
       <c r="R8" t="n">
-        <v>6818070</v>
+        <v>6817903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,14 +1425,19 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1447,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131047013</v>
+        <v>131046822</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,39 +1468,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401631</v>
+        <v>401699</v>
       </c>
       <c r="R9" t="n">
-        <v>6817903</v>
+        <v>6818070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,19 +1537,14 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046823</v>
+        <v>131046773</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,34 +1575,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401661</v>
+        <v>401346</v>
       </c>
       <c r="R10" t="n">
-        <v>6818064</v>
+        <v>6818162</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1639,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1649,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046773</v>
+        <v>131046823</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,39 +1692,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401346</v>
+        <v>401661</v>
       </c>
       <c r="R11" t="n">
-        <v>6818162</v>
+        <v>6818064</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,12 +1761,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,7 +1791,7 @@
         <v>131046828</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>131046769</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046771</v>
+        <v>131046709</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>83228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,39 +2023,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>401556</v>
+        <v>401646</v>
       </c>
       <c r="R14" t="n">
-        <v>6817954</v>
+        <v>6817967</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,7 +2082,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2097,12 +2092,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046709</v>
+        <v>131046771</v>
       </c>
       <c r="B15" t="n">
-        <v>83226</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,34 +2130,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401646</v>
+        <v>401556</v>
       </c>
       <c r="R15" t="n">
-        <v>6817967</v>
+        <v>6817954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2204,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046708</v>
+        <v>131046724</v>
       </c>
       <c r="B16" t="n">
-        <v>83226</v>
+        <v>79280</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401645</v>
+        <v>401635</v>
       </c>
       <c r="R16" t="n">
-        <v>6818016</v>
+        <v>6817874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131046724</v>
+        <v>131046708</v>
       </c>
       <c r="B17" t="n">
-        <v>79278</v>
+        <v>83228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401635</v>
+        <v>401645</v>
       </c>
       <c r="R17" t="n">
-        <v>6817874</v>
+        <v>6818016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131046827</v>
+        <v>131046768</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,34 +2461,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401630</v>
+        <v>401346</v>
       </c>
       <c r="R18" t="n">
-        <v>6817911</v>
+        <v>6818439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2525,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2535,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Både färska och gamla ringhack på grov gammal tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131046768</v>
+        <v>131046827</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,39 +2578,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>401346</v>
+        <v>401630</v>
       </c>
       <c r="R19" t="n">
-        <v>6818439</v>
+        <v>6817911</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Både färska och gamla ringhack på grov gammal tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131047034</v>
+        <v>131046799</v>
       </c>
       <c r="B20" t="n">
-        <v>78649</v>
+        <v>78260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401597</v>
+        <v>401649</v>
       </c>
       <c r="R20" t="n">
-        <v>6817852</v>
+        <v>6818014</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131046766</v>
+        <v>131047034</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>78651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,42 +2792,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401318</v>
+        <v>401597</v>
       </c>
       <c r="R21" t="n">
-        <v>6818379</v>
+        <v>6817852</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2859,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,12 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131046799</v>
+        <v>131046766</v>
       </c>
       <c r="B22" t="n">
-        <v>78258</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,34 +2899,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>401649</v>
+        <v>401318</v>
       </c>
       <c r="R22" t="n">
-        <v>6818014</v>
+        <v>6818379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2981,7 +2976,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131046833</v>
+        <v>131046831</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>401322</v>
+        <v>401378</v>
       </c>
       <c r="R23" t="n">
-        <v>6818367</v>
+        <v>6818089</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,10 +3115,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131046831</v>
+        <v>131046833</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401378</v>
+        <v>401322</v>
       </c>
       <c r="R24" t="n">
-        <v>6818089</v>
+        <v>6818367</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3225,7 +3225,7 @@
         <v>131046832</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131046826</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>131047014</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>131046770</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131046824</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131046825</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131046829</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131046765</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>131046830</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>131046772</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131047013</v>
+        <v>131046822</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,39 +1351,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401631</v>
+        <v>401699</v>
       </c>
       <c r="R8" t="n">
-        <v>6817903</v>
+        <v>6818070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,19 +1420,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1457,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046822</v>
+        <v>131047013</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,34 +1458,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401699</v>
+        <v>401631</v>
       </c>
       <c r="R9" t="n">
-        <v>6818070</v>
+        <v>6817903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,14 +1532,19 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046773</v>
+        <v>131046823</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,39 +1575,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401346</v>
+        <v>401661</v>
       </c>
       <c r="R10" t="n">
-        <v>6818162</v>
+        <v>6818064</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,12 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046823</v>
+        <v>131046773</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,34 +1682,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401661</v>
+        <v>401346</v>
       </c>
       <c r="R11" t="n">
-        <v>6818064</v>
+        <v>6818162</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,7 +1756,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,7 +1791,7 @@
         <v>131046828</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>131046769</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>131046709</v>
       </c>
       <c r="B14" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>131046771</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046724</v>
+        <v>131046708</v>
       </c>
       <c r="B16" t="n">
-        <v>79280</v>
+        <v>83229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401635</v>
+        <v>401645</v>
       </c>
       <c r="R16" t="n">
-        <v>6817874</v>
+        <v>6818016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131046708</v>
+        <v>131046724</v>
       </c>
       <c r="B17" t="n">
-        <v>83228</v>
+        <v>79281</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401645</v>
+        <v>401635</v>
       </c>
       <c r="R17" t="n">
-        <v>6818016</v>
+        <v>6817874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131046768</v>
+        <v>131046827</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,39 +2461,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401346</v>
+        <v>401630</v>
       </c>
       <c r="R18" t="n">
-        <v>6818439</v>
+        <v>6817911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2535,12 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Både färska och gamla ringhack på grov gammal tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131046827</v>
+        <v>131046768</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,34 +2568,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>401630</v>
+        <v>401346</v>
       </c>
       <c r="R19" t="n">
-        <v>6817911</v>
+        <v>6818439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Både färska och gamla ringhack på grov gammal tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131046799</v>
+        <v>131047034</v>
       </c>
       <c r="B20" t="n">
-        <v>78260</v>
+        <v>78652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401649</v>
+        <v>401597</v>
       </c>
       <c r="R20" t="n">
-        <v>6818014</v>
+        <v>6817852</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131047034</v>
+        <v>131046766</v>
       </c>
       <c r="B21" t="n">
-        <v>78651</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,34 +2792,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401597</v>
+        <v>401318</v>
       </c>
       <c r="R21" t="n">
-        <v>6817852</v>
+        <v>6818379</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2869,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131046766</v>
+        <v>131046799</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>78261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,42 +2912,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>401318</v>
+        <v>401649</v>
       </c>
       <c r="R22" t="n">
-        <v>6818379</v>
+        <v>6818014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,7 +2971,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2976,12 +2981,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3011,7 +3011,7 @@
         <v>131046831</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>131046833</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>131046832</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131046826</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>131047014</v>
       </c>
       <c r="B27" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>131046770</v>
       </c>
       <c r="B28" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046822</v>
+        <v>131047013</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,34 +1351,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401699</v>
+        <v>401631</v>
       </c>
       <c r="R8" t="n">
-        <v>6818070</v>
+        <v>6817903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,14 +1425,19 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1447,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131047013</v>
+        <v>131046822</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,39 +1468,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401631</v>
+        <v>401699</v>
       </c>
       <c r="R9" t="n">
-        <v>6817903</v>
+        <v>6818070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,19 +1537,14 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046708</v>
+        <v>131046724</v>
       </c>
       <c r="B16" t="n">
-        <v>83229</v>
+        <v>79281</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401645</v>
+        <v>401635</v>
       </c>
       <c r="R16" t="n">
-        <v>6818016</v>
+        <v>6817874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131046724</v>
+        <v>131046708</v>
       </c>
       <c r="B17" t="n">
-        <v>79281</v>
+        <v>83229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401635</v>
+        <v>401645</v>
       </c>
       <c r="R17" t="n">
-        <v>6817874</v>
+        <v>6818016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131046827</v>
+        <v>131046768</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,34 +2461,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401630</v>
+        <v>401346</v>
       </c>
       <c r="R18" t="n">
-        <v>6817911</v>
+        <v>6818439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2525,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2535,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Både färska och gamla ringhack på grov gammal tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131046768</v>
+        <v>131046827</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,39 +2578,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>401346</v>
+        <v>401630</v>
       </c>
       <c r="R19" t="n">
-        <v>6818439</v>
+        <v>6817911</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Både färska och gamla ringhack på grov gammal tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131047034</v>
+        <v>131046766</v>
       </c>
       <c r="B20" t="n">
-        <v>78652</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,34 +2685,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401597</v>
+        <v>401318</v>
       </c>
       <c r="R20" t="n">
-        <v>6817852</v>
+        <v>6818379</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2752,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2762,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131046766</v>
+        <v>131047034</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>78652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,42 +2805,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401318</v>
+        <v>401597</v>
       </c>
       <c r="R21" t="n">
-        <v>6818379</v>
+        <v>6817852</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2859,7 +2864,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,12 +2874,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1788,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046828</v>
+        <v>131046769</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,34 +1799,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401634</v>
+        <v>401575</v>
       </c>
       <c r="R12" t="n">
-        <v>6817871</v>
+        <v>6817873</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1873,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046769</v>
+        <v>131046828</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,39 +1916,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401575</v>
+        <v>401634</v>
       </c>
       <c r="R13" t="n">
-        <v>6817873</v>
+        <v>6817871</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,12 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131046766</v>
+        <v>131047034</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>78652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,42 +2685,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401318</v>
+        <v>401597</v>
       </c>
       <c r="R20" t="n">
-        <v>6818379</v>
+        <v>6817852</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2752,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,12 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2794,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131047034</v>
+        <v>131046766</v>
       </c>
       <c r="B21" t="n">
-        <v>78652</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,34 +2792,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401597</v>
+        <v>401318</v>
       </c>
       <c r="R21" t="n">
-        <v>6817852</v>
+        <v>6818379</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2874,7 +2869,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131046832</v>
+        <v>131047014</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,34 +3233,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401350</v>
+        <v>401378</v>
       </c>
       <c r="R25" t="n">
-        <v>6818162</v>
+        <v>6818082</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3292,7 +3297,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3302,14 +3307,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3329,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131046826</v>
+        <v>131046832</v>
       </c>
       <c r="B26" t="n">
         <v>79249</v>
@@ -3364,10 +3374,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401647</v>
+        <v>401350</v>
       </c>
       <c r="R26" t="n">
-        <v>6817965</v>
+        <v>6818162</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3399,7 +3409,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3409,7 +3419,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3436,10 +3446,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131047014</v>
+        <v>131046826</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,39 +3457,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401378</v>
+        <v>401647</v>
       </c>
       <c r="R27" t="n">
-        <v>6818082</v>
+        <v>6817965</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3511,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3521,19 +3526,14 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046724</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046822</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046823</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046824</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046825</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046826</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046827</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046828</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046829</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046830</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046831</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046832</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046833</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131047033</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131047034</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046708</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046709</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131047032</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2718,6 +2813,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046765</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2838,6 +2938,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046766</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2955,6 +3060,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046768</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3072,6 +3182,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046769</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3189,6 +3304,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046770</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3306,6 +3426,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046771</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3423,6 +3548,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046772</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3540,6 +3670,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046773</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3657,6 +3792,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131047013</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3774,6 +3914,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131047014</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3881,6 +4026,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046799</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3988,8 +4138,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131046731</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>